--- a/25b2244_q_1.xlsx
+++ b/25b2244_q_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gauri\DAV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{994D3BA7-9BBB-4600-A692-5F04D8751319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7340C9FA-7C82-49D1-81C4-8C5FBF241C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4987" uniqueCount="1053">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4985" uniqueCount="1051">
   <si>
     <t>Student_ID</t>
   </si>
@@ -3187,12 +3187,6 @@
   </si>
   <si>
     <t>Upper 95%</t>
-  </si>
-  <si>
-    <t>Lower 95.0%</t>
-  </si>
-  <si>
-    <t>Upper 95.0%</t>
   </si>
 </sst>
 </file>
@@ -3590,27 +3584,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD0AA89-0A01-460F-A4D8-7D6F16ACCC7C}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1029</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>1030</v>
       </c>
       <c r="B3" s="4"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1031</v>
       </c>
@@ -3618,7 +3614,7 @@
         <v>0.8838540288655663</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1032</v>
       </c>
@@ -3626,7 +3622,7 @@
         <v>0.78119794434189327</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>1033</v>
       </c>
@@ -3634,7 +3630,7 @@
         <v>0.77854579821270409</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>1034</v>
       </c>
@@ -3642,7 +3638,7 @@
         <v>7.931459763427779</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>1035</v>
       </c>
@@ -3650,12 +3646,12 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>1036</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>1041</v>
@@ -3673,7 +3669,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>1037</v>
       </c>
@@ -3693,7 +3689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>1038</v>
       </c>
@@ -3707,7 +3703,7 @@
         <v>62.908053978873838</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
         <v>1039</v>
       </c>
@@ -3721,8 +3717,8 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>1046</v>
@@ -3742,14 +3738,8 @@
       <c r="G16" s="3" t="s">
         <v>1050</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>1051</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>1040</v>
       </c>
@@ -3771,14 +3761,8 @@
       <c r="G17">
         <v>28.069305284559086</v>
       </c>
-      <c r="H17">
-        <v>14.603797470739416</v>
-      </c>
-      <c r="I17">
-        <v>28.069305284559086</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -3800,14 +3784,8 @@
       <c r="G18">
         <v>8.2053958567318581</v>
       </c>
-      <c r="H18">
-        <v>6.3391587497854012</v>
-      </c>
-      <c r="I18">
-        <v>8.2053958567318581</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -3829,14 +3807,8 @@
       <c r="G19">
         <v>-1.7782459784304332</v>
       </c>
-      <c r="H19">
-        <v>-3.6089433105631783</v>
-      </c>
-      <c r="I19">
-        <v>-1.7782459784304332</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -3858,14 +3830,8 @@
       <c r="G20">
         <v>-1.6645405619648548</v>
       </c>
-      <c r="H20">
-        <v>-3.4770867898763562</v>
-      </c>
-      <c r="I20">
-        <v>-1.6645405619648548</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -3887,14 +3853,8 @@
       <c r="G21">
         <v>0.7459032265820833</v>
       </c>
-      <c r="H21">
-        <v>-1.7073398005217888</v>
-      </c>
-      <c r="I21">
-        <v>0.7459032265820833</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -3916,14 +3876,8 @@
       <c r="G22">
         <v>0.17506665276550742</v>
       </c>
-      <c r="H22">
-        <v>6.5453807489254071E-2</v>
-      </c>
-      <c r="I22">
-        <v>0.17506665276550742</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -3945,14 +3899,8 @@
       <c r="G23">
         <v>-1.7085674309472867</v>
       </c>
-      <c r="H23">
-        <v>-3.2375584542014795</v>
-      </c>
-      <c r="I23">
-        <v>-1.7085674309472867</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -3974,14 +3922,8 @@
       <c r="G24">
         <v>-2.5064561586977336</v>
       </c>
-      <c r="H24">
-        <v>-4.2880162963749191</v>
-      </c>
-      <c r="I24">
-        <v>-2.5064561586977336</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -4003,14 +3945,8 @@
       <c r="G25">
         <v>9.1870575252564066</v>
       </c>
-      <c r="H25">
-        <v>7.4472957369170025</v>
-      </c>
-      <c r="I25">
-        <v>9.1870575252564066</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -4032,14 +3968,8 @@
       <c r="G26">
         <v>1.1459343904586967</v>
       </c>
-      <c r="H26">
-        <v>-1.0019272680822116</v>
-      </c>
-      <c r="I26">
-        <v>1.1459343904586967</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -4061,14 +3991,8 @@
       <c r="G27">
         <v>2.8679861169557341E-2</v>
       </c>
-      <c r="H27">
-        <v>-0.74497880560144603</v>
-      </c>
-      <c r="I27">
-        <v>2.8679861169557341E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -4090,14 +4014,8 @@
       <c r="G28">
         <v>2.0608244430136549</v>
       </c>
-      <c r="H28">
-        <v>-1.2283366814928089</v>
-      </c>
-      <c r="I28">
-        <v>2.0608244430136549</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="2" t="s">
         <v>18</v>
       </c>
@@ -4117,12 +4035,6 @@
         <v>-3.4306898031963518E-2</v>
       </c>
       <c r="G29" s="2">
-        <v>1.4739554196574449</v>
-      </c>
-      <c r="H29" s="2">
-        <v>-3.4306898031963518E-2</v>
-      </c>
-      <c r="I29" s="2">
         <v>1.4739554196574449</v>
       </c>
     </row>
